--- a/CV/CVcontent.xlsx
+++ b/CV/CVcontent.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSchmidt\Documents\GitHub\Schmidtpaul.github.io\CV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Schmidtpaul.github.io\CV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512C3018-2F41-4196-98BC-47F03A3B640D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71504D67-0397-42FF-B27E-C7B5C687E9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="180" windowWidth="30675" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Job" sheetId="1" r:id="rId1"/>
@@ -22,17 +22,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="153">
   <si>
     <t>BioMath - Applied Statistics and Informatics in Life Sciences</t>
   </si>
   <si>
-    <t>Rostock &amp; Hamburg, Germany</t>
-  </si>
-  <si>
-    <t>Implement new / streamline existing SOPs (for e.g. systematic literature reviews and meta-analyses) by making better use of in-depth functionality of established software and additionally via introducing complementing software/tools</t>
-  </si>
-  <si>
     <t>Freelancer (part-time)</t>
   </si>
   <si>
@@ -120,9 +114,6 @@
     <t>loc_ger</t>
   </si>
   <si>
-    <t>Rostock &amp; Hamburg</t>
-  </si>
-  <si>
     <t>Stuttgart</t>
   </si>
   <si>
@@ -135,15 +126,6 @@
     <t>details_ger</t>
   </si>
   <si>
-    <t>Geschäftsführer seit September 2022</t>
-  </si>
-  <si>
-    <t>General manager since September 2022</t>
-  </si>
-  <si>
-    <t>Implementierung neuer / Optimierung vorhandener SOPs (z.B. für systematic literature reviews und Metaanalysen), indem beispielsweise die Funktionalität vorhandener Software besser genutzt wird und zusätzlich ergänzende Software/Tools eingesetzt werden</t>
-  </si>
-  <si>
     <t>Durchführung von Workshops zu Statistik mit R; der genaue Inhalt und die Kurssprache in Absprache mit dem Auftraggeber</t>
   </si>
   <si>
@@ -306,12 +288,6 @@
     <t>German (native)</t>
   </si>
   <si>
-    <t>English (effective operational proficiency)</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
@@ -327,30 +303,6 @@
     <t>SQL</t>
   </si>
   <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>(generalized) linear (mixed) models</t>
-  </si>
-  <si>
-    <t>experimental design</t>
-  </si>
-  <si>
-    <t>Presentation</t>
-  </si>
-  <si>
-    <t>data visualization</t>
-  </si>
-  <si>
-    <t>data analysis reports</t>
-  </si>
-  <si>
-    <t>scientific publications</t>
-  </si>
-  <si>
-    <t>presentations</t>
-  </si>
-  <si>
     <t>Teamfähigkeit</t>
   </si>
   <si>
@@ -381,21 +333,9 @@
     <t>Deutsch (Muttersprache)</t>
   </si>
   <si>
-    <t>Englisch (kompetente, professionelle Sprachverwendung)</t>
-  </si>
-  <si>
-    <t>(generalisierte) lineare (gemischte) Modelle</t>
-  </si>
-  <si>
     <t>Versuchsdesign</t>
   </si>
   <si>
-    <t>Statistik</t>
-  </si>
-  <si>
-    <t>Präsentation</t>
-  </si>
-  <si>
     <t>Datenvisualisierung</t>
   </si>
   <si>
@@ -408,12 +348,6 @@
     <t>Präsentationen</t>
   </si>
   <si>
-    <t>exploratory &amp; descriptive data analysis</t>
-  </si>
-  <si>
-    <t>explorative &amp; deskriptive Datenauswertung</t>
-  </si>
-  <si>
     <t>content_ger</t>
   </si>
   <si>
@@ -441,25 +375,112 @@
     <t>R package CitaviR https://schmidtpaul.github.io/CitaviR/</t>
   </si>
   <si>
-    <t>Conduct systematic reviews, write and proofread scientific reports</t>
-  </si>
-  <si>
     <t>MS Office (VBA)</t>
   </si>
   <si>
-    <t>Various statistical analyses from raw data to final report, including conceptualization of research approach; data acquisition, cleansing, and integration; data analysis and modeling; interpretation, presentation, and communication of results.</t>
-  </si>
-  <si>
-    <t>Recent projects: Time series and correlation analysis of air parameters; Comparison of agricultural treatments; Co-creation and evaluation of monitoring surveys; Epidemiological risk assessments using meta-analyses; Evaluation of geographical distributions using GIS data.</t>
-  </si>
-  <si>
-    <t>Verschiedene statistische Analysen von Rohdaten bis Schlussbericht, d.h. Konzeption der Herangehensweise an die Fragestellung; Beschaffung, Bereinigung und Zusammenführung von Daten; Analyse und Modellierung; Interpretation, Aufbereitung und Vermittlung der Ergebnisse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kürzliche Projekte: Zeitreihen- und Zusammenhangsanalysen von Luftparametern; Vergleich von landwirtschaftlichen Behandlungen; Konzeption und Auswertung von Monitorings; Epidemiologische Risikobewertungen via Meta-Analyse; Geografischen Verteilungen mit GIS-Daten </t>
-  </si>
-  <si>
-    <t>Durchführung von Systematic Reviews und Verfassen und Korrekturlesen von wissenschaftlichen Texten</t>
+    <t>Hamburg, Germany</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>English (fluent)</t>
+  </si>
+  <si>
+    <t>Englisch (fließend)</t>
+  </si>
+  <si>
+    <t>Markdown</t>
+  </si>
+  <si>
+    <t>End-to-end Analytics: Fragestellungen präzisieren, Daten beschaffen/vereinheitlichen, Modelle entwickeln, Ergebnisse für Fach- und Management-Publikum übersetzen</t>
+  </si>
+  <si>
+    <t>Projekte (Auszug): Zeitreihen- und Regressionsanalysen von Luftparametern; Wirksamkeitsvergleiche in der Landwirtschaft; Monitoring-Designs &amp; -Auswertung; epidemiologische Meta-Analysen; räumliche Auswertungen mit GIS</t>
+  </si>
+  <si>
+    <t>SOPs skaliert (u. a. für Systematic Reviews &amp; Meta-Analysen): Toolchain konsolidiert, Automatisierung ausgebaut, Durchlaufzeiten reduziert und Reproduzierbarkeit erhöht</t>
+  </si>
+  <si>
+    <t>Systematic Reviews verantwortet; wissenschaftliche Texte verfasst, redigiert und publikationsreif gemacht</t>
+  </si>
+  <si>
+    <t>End-to-end analytics: clarify questions, acquire/align data, build models, translate results for both technical and executive audiences</t>
+  </si>
+  <si>
+    <t>Selected projects: time-series &amp; regression on air parameters; agricultural treatment comparisons; monitoring design &amp; evaluation; epidemiological meta-analyses; spatial analysis with GIS</t>
+  </si>
+  <si>
+    <t>Scaled SOPs (e.g., for systematic reviews &amp; meta-analyses): consolidated toolchain, added automation, improved reproducibility and cut cycle time</t>
+  </si>
+  <si>
+    <t>Systematic reviews led; authored, edited, and finalized scientific reports/publications</t>
+  </si>
+  <si>
+    <t>General manager since 2022</t>
+  </si>
+  <si>
+    <t>Geschäftsführer seit 2022</t>
+  </si>
+  <si>
+    <t>Analytics &amp; Statistics</t>
+  </si>
+  <si>
+    <t>(Generalized) Linear/Mixed Models</t>
+  </si>
+  <si>
+    <t>Experimental design</t>
+  </si>
+  <si>
+    <t>Exploratory &amp; descriptive analysis</t>
+  </si>
+  <si>
+    <t>Software &amp; Tools</t>
+  </si>
+  <si>
+    <t>Quarto/Markdown</t>
+  </si>
+  <si>
+    <t>Communication &amp; Impact</t>
+  </si>
+  <si>
+    <t>Executive-ready insights</t>
+  </si>
+  <si>
+    <t>Data visualization</t>
+  </si>
+  <si>
+    <t>Reports/scientific publications</t>
+  </si>
+  <si>
+    <t>Talks/workshops</t>
+  </si>
+  <si>
+    <t>LLM-assisted workflows</t>
+  </si>
+  <si>
+    <t>Explorative &amp; deskriptive Analysen</t>
+  </si>
+  <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>LLM-gestützte Produktivität</t>
+  </si>
+  <si>
+    <t>Analytics &amp; Statistik</t>
+  </si>
+  <si>
+    <t>Kommunikation &amp; Wirkung</t>
+  </si>
+  <si>
+    <t>Version Control (git)</t>
+  </si>
+  <si>
+    <t>reproducible pipelines &amp; DAG workflows</t>
+  </si>
+  <si>
+    <t>reproduzierbare Pipelines &amp; DAG-Workflows</t>
   </si>
 </sst>
 </file>
@@ -857,34 +878,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -893,10 +914,10 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>0</v>
@@ -905,16 +926,16 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -923,10 +944,10 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>0</v>
@@ -935,16 +956,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -953,10 +974,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>0</v>
@@ -965,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -983,10 +1004,10 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>0</v>
@@ -995,16 +1016,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1013,10 +1034,10 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>0</v>
@@ -1025,16 +1046,16 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1043,28 +1064,28 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1073,28 +1094,28 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>5</v>
-      </c>
       <c r="J8" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1105,28 +1126,28 @@
         <v>43465</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="H9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>9</v>
-      </c>
       <c r="J9" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1137,28 +1158,28 @@
         <v>43465</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="J10" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1169,28 +1190,28 @@
         <v>43465</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="H11" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1201,28 +1222,28 @@
         <v>43465</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="H12" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1233,10 +1254,10 @@
         <v>42246</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>0</v>
@@ -1245,16 +1266,16 @@
         <v>0</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1265,10 +1286,10 @@
         <v>42246</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>0</v>
@@ -1277,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="J14" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1330,34 +1351,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1368,28 +1389,28 @@
         <v>43799</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1400,28 +1421,28 @@
         <v>43799</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1432,28 +1453,28 @@
         <v>42369</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="H4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="J4" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1464,28 +1485,28 @@
         <v>42369</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1496,28 +1517,28 @@
         <v>42004</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1528,28 +1549,28 @@
         <v>42004</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1560,28 +1581,28 @@
         <v>41182</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1592,28 +1613,28 @@
         <v>41182</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1624,28 +1645,28 @@
         <v>39294</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1680,7 +1701,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D89F78D-EC1A-4292-B5B7-FAB02BA43469}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="14.7109375" style="3" customWidth="1"/>
@@ -1689,352 +1710,436 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>138</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>127</v>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/CV/CVcontent.xlsx
+++ b/CV/CVcontent.xlsx
@@ -1460,44 +1460,44 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -1508,10 +1508,10 @@
         <v>99</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -1522,10 +1522,10 @@
         <v>99</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -1536,80 +1536,80 @@
         <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1620,10 +1620,10 @@
         <v>137</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1634,10 +1634,10 @@
         <v>137</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -1648,10 +1648,10 @@
         <v>137</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1662,10 +1662,10 @@
         <v>137</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1676,10 +1676,10 @@
         <v>137</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1690,10 +1690,10 @@
         <v>137</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1704,10 +1704,10 @@
         <v>137</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1718,52 +1718,52 @@
         <v>137</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -1774,52 +1774,52 @@
         <v>148</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1830,51 +1830,9 @@
         <v>149</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="D31" s="5" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1944,11 +1902,15 @@
       <c r="H2" t="s">
         <v>167</v>
       </c>
-      <c r="I2" t="s">
-        <v>168</v>
-      </c>
-      <c r="J2" t="s">
-        <v>169</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-to-end analytics: clarify questions, acquire and align data, build models, and present results tailored to the audience</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-to-end Analytics: Fragestellungen präzisieren, Daten beschaffen und vereinheitlichen, Modelle entwickeln und Ergebnisse publikumsgerecht aufbereiten</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1974,11 +1936,15 @@
       <c r="H3" t="s">
         <v>167</v>
       </c>
-      <c r="I3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J3" t="s">
-        <v>171</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building and automating reproducible analysis and reporting pipelines in R and Python (Quarto)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufbau und Automatisierung reproduzierbarer Analyse- und Reporting-Pipelines in R und Python (Quarto)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2004,11 +1970,15 @@
       <c r="H4" t="s">
         <v>167</v>
       </c>
-      <c r="I4" t="s">
-        <v>172</v>
-      </c>
-      <c r="J4" t="s">
-        <v>173</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientific reports and publications, systematic reviews and meta-analyses</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wissenschaftliche Berichte und Publikationen, Systematic Reviews und Meta-Analysen</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -2035,40 +2005,40 @@
         <v>167</v>
       </c>
       <c r="I5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>43466</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F6" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G6" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="H6" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="I6" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="J6" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7">
@@ -2095,10 +2065,10 @@
         <v>182</v>
       </c>
       <c r="I7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
@@ -2125,10 +2095,10 @@
         <v>182</v>
       </c>
       <c r="I8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9">
@@ -2155,40 +2125,40 @@
         <v>182</v>
       </c>
       <c r="I9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46113</v>
+        <v>43405</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F10" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="G10" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="H10" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I10" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -2215,40 +2185,42 @@
         <v>196</v>
       </c>
       <c r="I11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>43405</v>
-      </c>
-      <c r="B12" s="7"/>
+        <v>42248</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>43465</v>
+      </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="D12" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="F12" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G12" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H12" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="I12" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="J12" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -2277,10 +2249,10 @@
         <v>204</v>
       </c>
       <c r="I13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
@@ -2309,10 +2281,10 @@
         <v>204</v>
       </c>
       <c r="I14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -2341,42 +2313,42 @@
         <v>204</v>
       </c>
       <c r="I15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>42248</v>
+        <v>42005</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>43465</v>
+        <v>42246</v>
       </c>
       <c r="C16" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E16" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="G16" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H16" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="I16" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J16" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
@@ -2405,41 +2377,9 @@
         <v>215</v>
       </c>
       <c r="I17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J17" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>42005</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>42246</v>
-      </c>
-      <c r="C18" t="s">
-        <v>213</v>
-      </c>
-      <c r="D18" t="s">
-        <v>213</v>
-      </c>
-      <c r="E18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F18" t="s">
-        <v>165</v>
-      </c>
-      <c r="G18" t="s">
-        <v>214</v>
-      </c>
-      <c r="H18" t="s">
-        <v>215</v>
-      </c>
-      <c r="I18" t="s">
-        <v>218</v>
-      </c>
-      <c r="J18" t="s">
         <v>219</v>
       </c>
     </row>
